--- a/AfterToken/Configs/GameConfig/Datas/battle.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/battle.xlsx
@@ -669,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,6 +863,66 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>9002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>11002</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11003</v>
+      </c>
+      <c r="E10" t="n">
+        <v>600</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
